--- a/data/dividends_info_20260824.xlsx
+++ b/data/dividends_info_20260824.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>42.84500122070312</v>
+        <v>42.22000122070312</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2100595108782751</v>
+        <v>0.2131691080005638</v>
       </c>
       <c r="J2" t="n">
         <v>203</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>66.34999847412109</v>
+        <v>66.40000152587891</v>
       </c>
       <c r="I3" t="n">
-        <v>1.055011327955079</v>
+        <v>1.054216843243867</v>
       </c>
       <c r="J3" t="n">
         <v>182</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.140000343322754</v>
+        <v>9.319999694824219</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6564551175737441</v>
+        <v>0.6437768451142812</v>
       </c>
       <c r="J4" t="n">
         <v>112</v>
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>42.84500122070312</v>
+        <v>42.22000122070312</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2100595108782751</v>
+        <v>0.2131691080005638</v>
       </c>
       <c r="J6" t="n">
         <v>112</v>
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.115000009536743</v>
+        <v>2.109999895095825</v>
       </c>
       <c r="I7" t="n">
-        <v>3.640661922118176</v>
+        <v>3.649289280960038</v>
       </c>
       <c r="J7" t="n">
         <v>91</v>
@@ -801,10 +801,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>24.1200008392334</v>
+        <v>23.53499984741211</v>
       </c>
       <c r="I8" t="n">
-        <v>1.119402946126023</v>
+        <v>1.14722754089879</v>
       </c>
       <c r="J8" t="n">
         <v>91</v>
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>22.59000015258789</v>
+        <v>22.46999931335449</v>
       </c>
       <c r="I9" t="n">
-        <v>2.611775104093614</v>
+        <v>2.625723266708548</v>
       </c>
       <c r="J9" t="n">
         <v>91</v>
@@ -895,10 +895,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5.75</v>
+        <v>5.840000152587891</v>
       </c>
       <c r="I10" t="n">
-        <v>3.478260869565217</v>
+        <v>3.424657444766908</v>
       </c>
       <c r="J10" t="n">
         <v>84</v>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.52000045776367</v>
+        <v>10.40999984741211</v>
       </c>
       <c r="I11" t="n">
-        <v>4.372623383875653</v>
+        <v>4.41882811472235</v>
       </c>
       <c r="J11" t="n">
         <v>63</v>
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7.650000095367432</v>
+        <v>7.400000095367432</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7843137157126817</v>
+        <v>0.8108108003614941</v>
       </c>
       <c r="J12" t="n">
         <v>56</v>
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5.039999961853027</v>
+        <v>4.980000019073486</v>
       </c>
       <c r="I15" t="n">
-        <v>0.753968259674922</v>
+        <v>0.7630522059128382</v>
       </c>
       <c r="J15" t="n">
         <v>35</v>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>24.1299991607666</v>
+        <v>23.53499984741211</v>
       </c>
       <c r="I16" t="n">
-        <v>1.118939118899755</v>
+        <v>1.14722754089879</v>
       </c>
       <c r="J16" t="n">
         <v>28</v>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>42.84500122070312</v>
+        <v>42.22000122070312</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2100595108782751</v>
+        <v>0.2131691080005638</v>
       </c>
       <c r="J18" t="n">
         <v>28</v>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>90.09999847412109</v>
+        <v>90.19999694824219</v>
       </c>
       <c r="I19" t="n">
-        <v>1.476137649860237</v>
+        <v>1.474501158534595</v>
       </c>
       <c r="J19" t="n">
         <v>28</v>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5.860000133514404</v>
+        <v>6</v>
       </c>
       <c r="I20" t="n">
-        <v>5.119453808272897</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
         <v>21</v>
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2.460000038146973</v>
+        <v>2.480000019073486</v>
       </c>
       <c r="I22" t="n">
-        <v>8.943089292214722</v>
+        <v>8.870967673709565</v>
       </c>
       <c r="J22" t="n">
         <v>-14</v>
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5.039999961853027</v>
+        <v>4.980000019073486</v>
       </c>
       <c r="I23" t="n">
-        <v>0.753968259674922</v>
+        <v>0.7630522059128382</v>
       </c>
       <c r="J23" t="n">
         <v>-21</v>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5.949999809265137</v>
+        <v>5.920000076293945</v>
       </c>
       <c r="I26" t="n">
-        <v>4.201680806959162</v>
+        <v>4.222972918549448</v>
       </c>
       <c r="J26" t="n">
         <v>-28</v>
@@ -3474,248 +3474,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Directa SIM S.P.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Directa SIM S.P.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ENTERA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ESI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Friends S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Lindbergh S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>OLIDATA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>OPS Italia S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>OVS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>PHILOGEN S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>VALTECNE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>